--- a/ig/DM-OCTOBRE-2024/CodeSystem-TRE-R214-SpecialiteUnite.xlsx
+++ b/ig/DM-OCTOBRE-2024/CodeSystem-TRE-R214-SpecialiteUnite.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20231215120000</t>
+    <t>20241025120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -52,7 +52,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>retired</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-15T12:00:00+01:00</t>
+    <t>2024-10-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
